--- a/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-05T10:09:20-03:00</t>
+    <t>2026-06-16T17:47:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -558,7 +558,7 @@
     <t>Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -613,7 +613,7 @@
     <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -673,7 +673,7 @@
   </si>
   <si>
     <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
     <t>Reported rather than primary record</t>
@@ -837,7 +837,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -915,7 +915,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1000,7 +1000,7 @@
     <t>MedicationRequest.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1040,7 +1040,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1068,7 +1068,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1210,7 +1210,7 @@
     <t>Identifies the type of individual that is desired to administer the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1295,7 +1295,7 @@
     <t>A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1316,7 +1316,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1366,7 +1366,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|MedicationRequest|4.0.1|ServiceRequest|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1415,7 +1415,7 @@
     <t>Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -1424,7 +1424,7 @@
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1568,7 +1568,7 @@
     <t>A coded concept identifying additional instructions such as "take with water" or "avoid operating heavy machinery".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.additionalInstruction</t>
@@ -2152,7 +2152,7 @@
     <t>Code for a known / defined timing pattern.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation</t>
+    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation|4.0.1</t>
   </si>
   <si>
     <t>Timing.code</t>
@@ -2200,7 +2200,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -2254,7 +2254,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -2692,7 +2692,7 @@
     <t>MedicationRequest.dosageInstruction.maxDosePerAdministration</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -3029,7 +3029,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -3052,7 +3052,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -3071,7 +3071,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
+++ b/docs/StructureDefinition-BRPrescricaoMedicamento.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
